--- a/Forecast_demand_data.xlsx
+++ b/Forecast_demand_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5e6b18ad1acc1266/Desktop/Vaccine_Tender/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="122" documentId="8_{90B69A98-A806-4331-9DFD-B75E3626E765}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CC12DDA2-7C2C-4A1B-9004-22E70F1C6A56}"/>
+  <xr:revisionPtr revIDLastSave="124" documentId="8_{90B69A98-A806-4331-9DFD-B75E3626E765}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F925C3EE-A2F7-40AB-A0D9-99C349ADA3CD}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{ADCB78BC-AF59-4031-B361-4F9BE8F7CC28}"/>
   </bookViews>
@@ -343,10 +343,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
